--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16.97288</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.61162</v>
+      </c>
+      <c r="E4" t="n">
         <v>16.62741</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.97288</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.61162</v>
       </c>
       <c r="F4" t="n">
         <v>42.15946</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>16.67285</v>
+      </c>
+      <c r="D6" t="n">
         <v>16.36078</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>16.52384</v>
-      </c>
-      <c r="E6" t="n">
-        <v>16.67285</v>
       </c>
       <c r="F6" t="n">
         <v>41.88231</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>16.9237</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16.5761</v>
+      </c>
+      <c r="E7" t="n">
         <v>16.69065</v>
-      </c>
-      <c r="D7" t="n">
-        <v>16.9237</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.5761</v>
       </c>
       <c r="F7" t="n">
         <v>41.48641</v>
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.63997</v>
+        <v>16.67742</v>
       </c>
       <c r="D9" t="n">
         <v>16.38919</v>
       </c>
       <c r="E9" t="n">
-        <v>16.67742</v>
+        <v>16.63997</v>
       </c>
       <c r="F9" t="n">
         <v>42.60643</v>
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.70038</v>
+        <v>16.9197</v>
       </c>
       <c r="D10" t="n">
         <v>16.13031</v>
       </c>
       <c r="E10" t="n">
-        <v>16.9197</v>
+        <v>16.70038</v>
       </c>
       <c r="F10" t="n">
         <v>42.26161</v>
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16.51448</v>
+        <v>16.5417</v>
       </c>
       <c r="D11" t="n">
         <v>16.18702</v>
       </c>
       <c r="E11" t="n">
-        <v>16.5417</v>
+        <v>16.51448</v>
       </c>
       <c r="F11" t="n">
         <v>43.23615</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>16.74289</v>
+      </c>
+      <c r="D12" t="n">
         <v>16.57836</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>16.65976</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.74289</v>
       </c>
       <c r="F12" t="n">
         <v>42.01478</v>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>16.79013</v>
+      </c>
+      <c r="D13" t="n">
         <v>16.42072</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>16.60559</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.79013</v>
       </c>
       <c r="F13" t="n">
         <v>43.23822</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.63704</v>
+        <v>16.85255</v>
       </c>
       <c r="D14" t="n">
         <v>16.26365</v>
       </c>
       <c r="E14" t="n">
-        <v>16.85255</v>
+        <v>16.63704</v>
       </c>
       <c r="F14" t="n">
         <v>43.12549</v>
@@ -810,13 +810,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.69881</v>
+        <v>16.77676</v>
       </c>
       <c r="D16" t="n">
         <v>16.6373</v>
       </c>
       <c r="E16" t="n">
-        <v>16.77676</v>
+        <v>16.69881</v>
       </c>
       <c r="F16" t="n">
         <v>42.46084</v>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>16.88736</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.34641</v>
+      </c>
+      <c r="E18" t="n">
         <v>16.8187</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16.88736</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.34641</v>
       </c>
       <c r="F18" t="n">
         <v>42.51925</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.68458</v>
+        <v>16.68966</v>
       </c>
       <c r="D20" t="n">
         <v>16.49039</v>
       </c>
       <c r="E20" t="n">
-        <v>16.68966</v>
+        <v>16.68458</v>
       </c>
       <c r="F20" t="n">
         <v>41.14008</v>
@@ -938,10 +938,10 @@
         <v>16.86202</v>
       </c>
       <c r="D21" t="n">
+        <v>16.1748</v>
+      </c>
+      <c r="E21" t="n">
         <v>16.36145</v>
-      </c>
-      <c r="E21" t="n">
-        <v>16.1748</v>
       </c>
       <c r="F21" t="n">
         <v>42.37609</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>16.62128</v>
+      </c>
+      <c r="D22" t="n">
         <v>16.32475</v>
-      </c>
-      <c r="D22" t="n">
-        <v>16.62128</v>
       </c>
       <c r="E22" t="n">
         <v>16.329</v>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.60441</v>
+        <v>16.64846</v>
       </c>
       <c r="D23" t="n">
         <v>16.38601</v>
       </c>
       <c r="E23" t="n">
-        <v>16.64846</v>
+        <v>16.60441</v>
       </c>
       <c r="F23" t="n">
         <v>41.91358</v>
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.65725</v>
+        <v>16.90834</v>
       </c>
       <c r="D24" t="n">
         <v>16.65591</v>
       </c>
       <c r="E24" t="n">
-        <v>16.90834</v>
+        <v>16.65725</v>
       </c>
       <c r="F24" t="n">
         <v>42.10634</v>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>16.67408</v>
+      </c>
+      <c r="D26" t="n">
         <v>16.31269</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>16.43608</v>
-      </c>
-      <c r="E26" t="n">
-        <v>16.67408</v>
       </c>
       <c r="F26" t="n">
         <v>42.86411</v>
@@ -1088,10 +1088,10 @@
         <v>16.68353</v>
       </c>
       <c r="D27" t="n">
+        <v>16.59584</v>
+      </c>
+      <c r="E27" t="n">
         <v>16.61826</v>
-      </c>
-      <c r="E27" t="n">
-        <v>16.59584</v>
       </c>
       <c r="F27" t="n">
         <v>42.18798</v>
@@ -1113,10 +1113,10 @@
         <v>16.91689</v>
       </c>
       <c r="D28" t="n">
+        <v>16.34772</v>
+      </c>
+      <c r="E28" t="n">
         <v>16.38735</v>
-      </c>
-      <c r="E28" t="n">
-        <v>16.34772</v>
       </c>
       <c r="F28" t="n">
         <v>42.50738</v>
@@ -1138,10 +1138,10 @@
         <v>16.92716</v>
       </c>
       <c r="D29" t="n">
+        <v>16.6058</v>
+      </c>
+      <c r="E29" t="n">
         <v>16.68056</v>
-      </c>
-      <c r="E29" t="n">
-        <v>16.6058</v>
       </c>
       <c r="F29" t="n">
         <v>41.56678</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>16.73434</v>
+      </c>
+      <c r="D31" t="n">
         <v>16.41233</v>
-      </c>
-      <c r="D31" t="n">
-        <v>16.73434</v>
       </c>
       <c r="E31" t="n">
         <v>16.52923</v>
@@ -1210,13 +1210,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.62884</v>
+        <v>16.6669</v>
       </c>
       <c r="D32" t="n">
         <v>16.47349</v>
       </c>
       <c r="E32" t="n">
-        <v>16.6669</v>
+        <v>16.62884</v>
       </c>
       <c r="F32" t="n">
         <v>41.79841</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>16.92831</v>
+      </c>
+      <c r="D33" t="n">
         <v>16.50458</v>
-      </c>
-      <c r="D33" t="n">
-        <v>16.92831</v>
       </c>
       <c r="E33" t="n">
         <v>16.74254</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.60455</v>
+        <v>16.9535</v>
       </c>
       <c r="D34" t="n">
         <v>16.54199</v>
       </c>
       <c r="E34" t="n">
-        <v>16.9535</v>
+        <v>16.60455</v>
       </c>
       <c r="F34" t="n">
         <v>43.24859</v>
@@ -1310,13 +1310,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.76478</v>
+        <v>16.91159</v>
       </c>
       <c r="D36" t="n">
         <v>16.15521</v>
       </c>
       <c r="E36" t="n">
-        <v>16.91159</v>
+        <v>16.76478</v>
       </c>
       <c r="F36" t="n">
         <v>41.81956</v>
@@ -1338,10 +1338,10 @@
         <v>16.72139</v>
       </c>
       <c r="D37" t="n">
+        <v>16.51388</v>
+      </c>
+      <c r="E37" t="n">
         <v>16.63948</v>
-      </c>
-      <c r="E37" t="n">
-        <v>16.51388</v>
       </c>
       <c r="F37" t="n">
         <v>42.5207</v>
@@ -1417,10 +1417,10 @@
         <v>16.72529</v>
       </c>
       <c r="D40" t="n">
+        <v>15.82401</v>
+      </c>
+      <c r="E40" t="n">
         <v>16.11704</v>
-      </c>
-      <c r="E40" t="n">
-        <v>15.82401</v>
       </c>
       <c r="F40" t="n">
         <v>21.47622</v>
@@ -1659,10 +1659,10 @@
         <v>16.60669</v>
       </c>
       <c r="D51" t="n">
+        <v>15.97086</v>
+      </c>
+      <c r="E51" t="n">
         <v>16.15308</v>
-      </c>
-      <c r="E51" t="n">
-        <v>15.97086</v>
       </c>
       <c r="F51" t="n">
         <v>21.41967</v>
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16.5134</v>
+        <v>16.5421</v>
       </c>
       <c r="D52" t="n">
         <v>15.83472</v>
       </c>
       <c r="E52" t="n">
-        <v>16.5421</v>
+        <v>16.5134</v>
       </c>
       <c r="F52" t="n">
         <v>21.8425</v>
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>16.50075</v>
+        <v>16.51779</v>
       </c>
       <c r="D64" t="n">
         <v>15.63683</v>
       </c>
       <c r="E64" t="n">
-        <v>16.51779</v>
+        <v>16.50075</v>
       </c>
       <c r="F64" t="n">
         <v>21.22157</v>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>16.33047</v>
+        <v>16.37409</v>
       </c>
       <c r="D70" t="n">
         <v>15.97749</v>
       </c>
       <c r="E70" t="n">
-        <v>16.37409</v>
+        <v>16.33047</v>
       </c>
       <c r="F70" t="n">
         <v>21.6327</v>
@@ -2099,10 +2099,10 @@
         <v>16.55633</v>
       </c>
       <c r="D71" t="n">
+        <v>16.03689</v>
+      </c>
+      <c r="E71" t="n">
         <v>16.14627</v>
-      </c>
-      <c r="E71" t="n">
-        <v>16.03689</v>
       </c>
       <c r="F71" t="n">
         <v>21.82254</v>
